--- a/consolidacion/data/pruebas/viviendas_jornada4_20260816_0700.xlsx
+++ b/consolidacion/data/pruebas/viviendas_jornada4_20260816_0700.xlsx
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
